--- a/MTTO_Preventivo_Termoformado_2026.xlsx
+++ b/MTTO_Preventivo_Termoformado_2026.xlsx
@@ -2526,9 +2526,9 @@
       </c>
       <c r="O2" s="140" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
     </row>
@@ -2659,9 +2659,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -4111,9 +4111,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -5092,9 +5092,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -6077,9 +6077,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -7058,9 +7058,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -8030,9 +8030,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -9034,9 +9034,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -10679,9 +10679,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -12324,9 +12324,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -13969,9 +13969,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -15614,9 +15614,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -17259,9 +17259,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -18904,9 +18904,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>
@@ -20557,9 +20557,9 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento    A3.I1.F2
-Revision:                    00
-Fecha:                         08/06/2026</t>
+          <t>No. de Documento             A9.I1.F2
+Revision:                                    00
+Fecha:                        08/06/2026</t>
         </is>
       </c>
       <c r="P2" s="110" t="n"/>

--- a/MTTO_Preventivo_Termoformado_2026.xlsx
+++ b/MTTO_Preventivo_Termoformado_2026.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O2" s="140" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -2659,7 +2659,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -4111,7 +4111,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -5092,7 +5092,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -6077,7 +6077,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -7058,7 +7058,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -8030,7 +8030,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -9034,7 +9034,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -10679,7 +10679,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -12324,7 +12324,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -13969,7 +13969,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -15614,7 +15614,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -17259,7 +17259,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -18904,7 +18904,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="141" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
@@ -20557,7 +20557,7 @@
       <c r="N2" s="111" t="n"/>
       <c r="O2" s="144" t="inlineStr">
         <is>
-          <t>No. de Documento             A9.I1.F2
+          <t>No. de Documento             A9.I1.F1
 Revision:                                    00
 Fecha:                        08/06/2026</t>
         </is>
